--- a/jogos_2024-12-20.xlsx
+++ b/jogos_2024-12-20.xlsx
@@ -1020,7 +1020,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1030,25 +1030,25 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>Ironi Ramat HaSharon</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -1056,83 +1056,83 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M5" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N5" t="n">
         <v>3.1</v>
       </c>
-      <c r="N5" t="n">
-        <v>1.6</v>
-      </c>
       <c r="O5" t="n">
-        <v>7</v>
+        <v>2.6</v>
       </c>
       <c r="P5" t="n">
-        <v>1.83</v>
+        <v>2.3</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.38</v>
+        <v>3.5</v>
       </c>
       <c r="R5" t="n">
-        <v>1.62</v>
+        <v>1.33</v>
       </c>
       <c r="S5" t="n">
-        <v>2.2</v>
+        <v>3.25</v>
       </c>
       <c r="T5" t="n">
-        <v>4</v>
+        <v>2.63</v>
       </c>
       <c r="U5" t="n">
-        <v>1.2</v>
+        <v>1.44</v>
       </c>
       <c r="V5" t="n">
-        <v>1.13</v>
+        <v>1.01</v>
       </c>
       <c r="W5" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="X5" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="Y5" t="n">
         <v>1.67</v>
       </c>
-      <c r="X5" t="n">
+      <c r="Z5" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AA5" t="n">
         <v>2.1</v>
       </c>
-      <c r="Y5" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>6.5</v>
-      </c>
       <c r="AB5" t="n">
-        <v>1.1</v>
+        <v>1.65</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.63</v>
+        <v>1.57</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.44</v>
+        <v>2.25</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['25']</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>['81']</t>
+          <t>['21', '42', '90']</t>
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>1.83</v>
+        <v>1.3</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.12</v>
+        <v>1.56</v>
       </c>
       <c r="AI5" t="n">
-        <v>4.33</v>
+        <v>1.67</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1.44</v>
+        <v>2.3</v>
       </c>
       <c r="AK5" s="3" t="n">
         <v>45646.41666666666</v>
@@ -1159,25 +1159,25 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -1188,80 +1188,80 @@
         <v>2.5</v>
       </c>
       <c r="M6" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="N6" t="n">
-        <v>2.45</v>
+        <v>2.55</v>
       </c>
       <c r="O6" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="P6" t="n">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="Q6" t="n">
         <v>3.1</v>
       </c>
       <c r="R6" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="S6" t="n">
-        <v>2.63</v>
+        <v>2.75</v>
       </c>
       <c r="T6" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V6" t="n">
+        <v>1</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="X6" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA6" t="n">
         <v>3</v>
       </c>
-      <c r="U6" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V6" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W6" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="X6" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="Y6" t="n">
+      <c r="AB6" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG6" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AJ6" t="n">
         <v>2.05</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AE6" t="inlineStr">
-        <is>
-          <t>['61', '67']</t>
-        </is>
-      </c>
-      <c r="AF6" t="inlineStr">
-        <is>
-          <t>['29']</t>
-        </is>
-      </c>
-      <c r="AG6" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>1.83</v>
       </c>
       <c r="AK6" s="3" t="n">
         <v>45646.41666666666</v>
@@ -1278,7 +1278,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1288,25 +1288,25 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
         <v>1</v>
       </c>
       <c r="J7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -1314,83 +1314,83 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.4</v>
+        <v>1.57</v>
       </c>
       <c r="M7" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="N7" t="n">
-        <v>2.6</v>
+        <v>6.5</v>
       </c>
       <c r="O7" t="n">
-        <v>3</v>
+        <v>2.3</v>
       </c>
       <c r="P7" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.2</v>
+        <v>8</v>
       </c>
       <c r="R7" t="n">
-        <v>1.36</v>
+        <v>1.67</v>
       </c>
       <c r="S7" t="n">
-        <v>3</v>
+        <v>2.1</v>
       </c>
       <c r="T7" t="n">
-        <v>2.75</v>
+        <v>4.5</v>
       </c>
       <c r="U7" t="n">
-        <v>1.4</v>
+        <v>1.17</v>
       </c>
       <c r="V7" t="n">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="W7" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="X7" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>['30', '77', '90+1']</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG7" t="n">
         <v>1.22</v>
       </c>
-      <c r="X7" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>2</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AE7" t="inlineStr">
-        <is>
-          <t>['32']</t>
-        </is>
-      </c>
-      <c r="AF7" t="inlineStr">
-        <is>
-          <t>['45+1']</t>
-        </is>
-      </c>
-      <c r="AG7" t="n">
-        <v>1.37</v>
-      </c>
       <c r="AH7" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AI7" t="n">
         <v>1.44</v>
       </c>
-      <c r="AI7" t="n">
-        <v>1.83</v>
-      </c>
       <c r="AJ7" t="n">
-        <v>2.1</v>
+        <v>5</v>
       </c>
       <c r="AK7" s="3" t="n">
         <v>45646.41666666666</v>
@@ -1407,7 +1407,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,16 +1417,16 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Havadar</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Nassaji Mazandaran</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H8" t="n">
         <v>1</v>
@@ -1435,7 +1435,7 @@
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -1443,80 +1443,80 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>3.45</v>
+        <v>2.5</v>
       </c>
       <c r="M8" t="n">
-        <v>2.65</v>
+        <v>3.25</v>
       </c>
       <c r="N8" t="n">
-        <v>2.3</v>
+        <v>2.45</v>
       </c>
       <c r="O8" t="n">
-        <v>4.5</v>
+        <v>3.25</v>
       </c>
       <c r="P8" t="n">
-        <v>1.8</v>
+        <v>2.05</v>
       </c>
       <c r="Q8" t="n">
         <v>3.1</v>
       </c>
       <c r="R8" t="n">
-        <v>1.59</v>
+        <v>1.44</v>
       </c>
       <c r="S8" t="n">
-        <v>2.27</v>
+        <v>2.63</v>
       </c>
       <c r="T8" t="n">
-        <v>3.7</v>
+        <v>3</v>
       </c>
       <c r="U8" t="n">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="V8" t="n">
-        <v>1.09</v>
+        <v>1.03</v>
       </c>
       <c r="W8" t="n">
-        <v>1.53</v>
+        <v>1.39</v>
       </c>
       <c r="X8" t="n">
-        <v>2.25</v>
+        <v>2.75</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.6</v>
+        <v>2.05</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.44</v>
+        <v>1.75</v>
       </c>
       <c r="AA8" t="n">
-        <v>4.7</v>
+        <v>3.95</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.12</v>
+        <v>1.21</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.4</v>
+        <v>1.83</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.54</v>
+        <v>1.83</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['61', '67']</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>['78']</t>
+          <t>['29']</t>
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>1.3</v>
+        <v>1.39</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.53</v>
+        <v>1.38</v>
       </c>
       <c r="AI8" t="n">
-        <v>2.88</v>
+        <v>2.1</v>
       </c>
       <c r="AJ8" t="n">
         <v>1.83</v>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,22 +1546,22 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>Havadar</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Nassaji Mazandaran</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1572,83 +1572,83 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.57</v>
+        <v>3.45</v>
       </c>
       <c r="M9" t="n">
-        <v>3.1</v>
+        <v>2.65</v>
       </c>
       <c r="N9" t="n">
-        <v>6.5</v>
+        <v>2.3</v>
       </c>
       <c r="O9" t="n">
-        <v>2.3</v>
+        <v>4.5</v>
       </c>
       <c r="P9" t="n">
         <v>1.8</v>
       </c>
       <c r="Q9" t="n">
-        <v>8</v>
+        <v>3.1</v>
       </c>
       <c r="R9" t="n">
-        <v>1.67</v>
+        <v>1.59</v>
       </c>
       <c r="S9" t="n">
-        <v>2.1</v>
+        <v>2.27</v>
       </c>
       <c r="T9" t="n">
-        <v>4.5</v>
+        <v>3.7</v>
       </c>
       <c r="U9" t="n">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="V9" t="n">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="W9" t="n">
-        <v>1.75</v>
+        <v>1.53</v>
       </c>
       <c r="X9" t="n">
-        <v>1.95</v>
+        <v>2.25</v>
       </c>
       <c r="Y9" t="n">
-        <v>3.25</v>
+        <v>2.6</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="AA9" t="n">
-        <v>6.5</v>
+        <v>4.7</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="AC9" t="n">
-        <v>3.1</v>
+        <v>2.4</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.33</v>
+        <v>1.54</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>['30', '77', '90+1']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['78']</t>
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="AI9" t="n">
-        <v>1.44</v>
+        <v>2.88</v>
       </c>
       <c r="AJ9" t="n">
-        <v>5</v>
+        <v>1.83</v>
       </c>
       <c r="AK9" s="3" t="n">
         <v>45646.41666666666</v>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1822,7 +1822,7 @@
         <v>1</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -1830,61 +1830,61 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.15</v>
+        <v>2.4</v>
       </c>
       <c r="M11" t="n">
-        <v>2.8</v>
+        <v>3.2</v>
       </c>
       <c r="N11" t="n">
-        <v>3.6</v>
+        <v>2.6</v>
       </c>
       <c r="O11" t="n">
         <v>3</v>
       </c>
       <c r="P11" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S11" t="n">
+        <v>3</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="X11" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="Y11" t="n">
         <v>1.8</v>
       </c>
-      <c r="Q11" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="S11" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="T11" t="n">
-        <v>4</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="V11" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="X11" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>2.64</v>
-      </c>
       <c r="Z11" t="n">
-        <v>1.4</v>
+        <v>2</v>
       </c>
       <c r="AA11" t="n">
-        <v>6</v>
+        <v>2.7</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.13</v>
+        <v>1.41</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.38</v>
+        <v>1.67</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.53</v>
+        <v>2.1</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
@@ -1893,20 +1893,20 @@
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>['50']</t>
+          <t>['45+1']</t>
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>1.29</v>
+        <v>1.37</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="AI11" t="n">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AJ11" t="n">
-        <v>2.88</v>
+        <v>2.1</v>
       </c>
       <c r="AK11" s="3" t="n">
         <v>45646.41666666666</v>
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,16 +1933,16 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Hapoel Umm al-Fahm</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Hapoel Petah Tikva</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H12" t="n">
         <v>1</v>
@@ -1951,7 +1951,7 @@
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -1959,83 +1959,83 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>5.5</v>
+        <v>3.7</v>
       </c>
       <c r="M12" t="n">
-        <v>4</v>
+        <v>2.8</v>
       </c>
       <c r="N12" t="n">
-        <v>1.48</v>
+        <v>2.1</v>
       </c>
       <c r="O12" t="n">
-        <v>5.5</v>
+        <v>4.5</v>
       </c>
       <c r="P12" t="n">
-        <v>2.3</v>
+        <v>1.8</v>
       </c>
       <c r="Q12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S12" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="T12" t="n">
+        <v>3.46</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="X12" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="Z12" t="n">
         <v>1.4</v>
       </c>
-      <c r="S12" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="T12" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U12" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V12" t="n">
-        <v>1</v>
-      </c>
-      <c r="W12" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="X12" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>2.05</v>
-      </c>
       <c r="AA12" t="n">
-        <v>2.9</v>
+        <v>4.4</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.36</v>
+        <v>1.14</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.91</v>
+        <v>2.38</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.8</v>
+        <v>1.55</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['63']</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>['78']</t>
+          <t>['45+3']</t>
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>2.16</v>
+        <v>1.22</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.11</v>
+        <v>1.72</v>
       </c>
       <c r="AI12" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="AJ12" t="n">
-        <v>1.36</v>
+        <v>1.73</v>
       </c>
       <c r="AK12" s="3" t="n">
         <v>45646.41666666666</v>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,19 +2062,19 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="G13" t="n">
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
@@ -2088,61 +2088,61 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.5</v>
+        <v>6</v>
       </c>
       <c r="M13" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="N13" t="n">
-        <v>2.55</v>
+        <v>1.6</v>
       </c>
       <c r="O13" t="n">
-        <v>3.1</v>
+        <v>7</v>
       </c>
       <c r="P13" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="S13" t="n">
         <v>2.2</v>
       </c>
-      <c r="Q13" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="R13" t="n">
+      <c r="T13" t="n">
+        <v>4</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="X13" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="Z13" t="n">
         <v>1.4</v>
       </c>
-      <c r="S13" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="T13" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U13" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V13" t="n">
-        <v>1</v>
-      </c>
-      <c r="W13" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="X13" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>2</v>
-      </c>
       <c r="AA13" t="n">
-        <v>3</v>
+        <v>6.5</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.34</v>
+        <v>1.1</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.62</v>
+        <v>2.63</v>
       </c>
       <c r="AD13" t="n">
-        <v>2.2</v>
+        <v>1.44</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
@@ -2151,20 +2151,20 @@
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['81']</t>
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>1.35</v>
+        <v>1.83</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.47</v>
+        <v>1.12</v>
       </c>
       <c r="AI13" t="n">
-        <v>1.83</v>
+        <v>4.33</v>
       </c>
       <c r="AJ13" t="n">
-        <v>2.05</v>
+        <v>1.44</v>
       </c>
       <c r="AK13" s="3" t="n">
         <v>45646.41666666666</v>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2206,10 +2206,10 @@
         <v>1</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -2217,83 +2217,83 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>3.7</v>
+        <v>2.15</v>
       </c>
       <c r="M14" t="n">
         <v>2.8</v>
       </c>
       <c r="N14" t="n">
-        <v>2.1</v>
+        <v>3.6</v>
       </c>
       <c r="O14" t="n">
-        <v>4.5</v>
+        <v>3</v>
       </c>
       <c r="P14" t="n">
         <v>1.8</v>
       </c>
       <c r="Q14" t="n">
-        <v>3</v>
+        <v>4.5</v>
       </c>
       <c r="R14" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="S14" t="n">
-        <v>2.48</v>
+        <v>2.25</v>
       </c>
       <c r="T14" t="n">
-        <v>3.46</v>
+        <v>4</v>
       </c>
       <c r="U14" t="n">
-        <v>1.28</v>
+        <v>1.2</v>
       </c>
       <c r="V14" t="n">
-        <v>1.03</v>
+        <v>1.13</v>
       </c>
       <c r="W14" t="n">
-        <v>1.39</v>
+        <v>1.59</v>
       </c>
       <c r="X14" t="n">
-        <v>2.59</v>
+        <v>2.2</v>
       </c>
       <c r="Y14" t="n">
-        <v>2.75</v>
+        <v>2.64</v>
       </c>
       <c r="Z14" t="n">
         <v>1.4</v>
       </c>
       <c r="AA14" t="n">
-        <v>4.4</v>
+        <v>6</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AC14" t="n">
         <v>2.38</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>['63']</t>
+          <t>['32']</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>['45+3']</t>
+          <t>['50']</t>
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.72</v>
+        <v>1.53</v>
       </c>
       <c r="AI14" t="n">
-        <v>3</v>
+        <v>1.73</v>
       </c>
       <c r="AJ14" t="n">
-        <v>1.73</v>
+        <v>2.88</v>
       </c>
       <c r="AK14" s="3" t="n">
         <v>45646.41666666666</v>
@@ -2320,25 +2320,25 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Hapoel Umm al-Fahm</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ironi Ramat HaSharon</t>
+          <t>Hapoel Petah Tikva</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -2346,83 +2346,83 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2</v>
+        <v>5.5</v>
       </c>
       <c r="M15" t="n">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="N15" t="n">
-        <v>3.1</v>
+        <v>1.48</v>
       </c>
       <c r="O15" t="n">
-        <v>2.6</v>
+        <v>5.5</v>
       </c>
       <c r="P15" t="n">
         <v>2.3</v>
       </c>
       <c r="Q15" t="n">
+        <v>2</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S15" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="X15" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AE15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF15" t="inlineStr">
+        <is>
+          <t>['78']</t>
+        </is>
+      </c>
+      <c r="AG15" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AI15" t="n">
         <v>3.5</v>
       </c>
-      <c r="R15" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S15" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="T15" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="U15" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="V15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="X15" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AE15" t="inlineStr">
-        <is>
-          <t>['25']</t>
-        </is>
-      </c>
-      <c r="AF15" t="inlineStr">
-        <is>
-          <t>['21', '42', '90']</t>
-        </is>
-      </c>
-      <c r="AG15" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>1.67</v>
-      </c>
       <c r="AJ15" t="n">
-        <v>2.3</v>
+        <v>1.36</v>
       </c>
       <c r="AK15" s="3" t="n">
         <v>45646.41666666666</v>
@@ -3084,7 +3084,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,25 +3094,25 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Sepsi</t>
+          <t>Osijek</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
@@ -3120,83 +3120,83 @@
         </is>
       </c>
       <c r="L21" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="M21" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="N21" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="O21" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="P21" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S21" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="V21" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="X21" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AA21" t="n">
         <v>3.2</v>
       </c>
-      <c r="M21" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="N21" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="O21" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="P21" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="R21" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="S21" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="T21" t="n">
-        <v>3.48</v>
-      </c>
-      <c r="U21" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="V21" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="W21" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="X21" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>4.4</v>
-      </c>
       <c r="AB21" t="n">
-        <v>1.18</v>
+        <v>1.3</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.02</v>
+        <v>1.91</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.74</v>
+        <v>1.8</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['64', '67']</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['37', '60']</t>
         </is>
       </c>
       <c r="AG21" t="n">
-        <v>1.36</v>
+        <v>1.15</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.43</v>
+        <v>2.2</v>
       </c>
       <c r="AI21" t="n">
-        <v>2.06</v>
+        <v>1.4</v>
       </c>
       <c r="AJ21" t="n">
-        <v>2.19</v>
+        <v>3.25</v>
       </c>
       <c r="AK21" s="3" t="n">
         <v>45646.58333333334</v>
@@ -3213,7 +3213,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3223,25 +3223,25 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Osijek</t>
+          <t>Sepsi</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I22" t="n">
         <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
@@ -3249,83 +3249,83 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.6</v>
+        <v>3.2</v>
       </c>
       <c r="M22" t="n">
-        <v>3.75</v>
+        <v>2.95</v>
       </c>
       <c r="N22" t="n">
-        <v>5.25</v>
+        <v>2.25</v>
       </c>
       <c r="O22" t="n">
-        <v>2.25</v>
+        <v>3.3</v>
       </c>
       <c r="P22" t="n">
-        <v>2.2</v>
+        <v>1.92</v>
       </c>
       <c r="Q22" t="n">
-        <v>5.5</v>
+        <v>3.65</v>
       </c>
       <c r="R22" t="n">
-        <v>1.35</v>
+        <v>1.54</v>
       </c>
       <c r="S22" t="n">
-        <v>3.06</v>
+        <v>2.35</v>
       </c>
       <c r="T22" t="n">
-        <v>2.79</v>
+        <v>3.48</v>
       </c>
       <c r="U22" t="n">
-        <v>1.41</v>
+        <v>1.28</v>
       </c>
       <c r="V22" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="W22" t="n">
-        <v>1.22</v>
+        <v>1.45</v>
       </c>
       <c r="X22" t="n">
-        <v>3.8</v>
+        <v>2.6</v>
       </c>
       <c r="Y22" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="Z22" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="AA22" t="n">
-        <v>3.2</v>
+        <v>4.4</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.91</v>
+        <v>2.02</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.8</v>
+        <v>1.74</v>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>['64', '67']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>['37', '60']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>1.15</v>
+        <v>1.36</v>
       </c>
       <c r="AH22" t="n">
-        <v>2.2</v>
+        <v>1.43</v>
       </c>
       <c r="AI22" t="n">
-        <v>1.4</v>
+        <v>2.06</v>
       </c>
       <c r="AJ22" t="n">
-        <v>3.25</v>
+        <v>2.19</v>
       </c>
       <c r="AK22" s="3" t="n">
         <v>45646.58333333334</v>
@@ -3729,7 +3729,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3739,22 +3739,22 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Leixões</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>CD Mafra</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="G26" t="n">
+        <v>1</v>
+      </c>
+      <c r="H26" t="n">
         <v>2</v>
       </c>
-      <c r="H26" t="n">
-        <v>1</v>
-      </c>
       <c r="I26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J26" t="n">
         <v>1</v>
@@ -3765,83 +3765,83 @@
         </is>
       </c>
       <c r="L26" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="M26" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="N26" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="O26" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="P26" t="n">
         <v>1.8</v>
       </c>
-      <c r="M26" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="N26" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="O26" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="P26" t="n">
-        <v>1.97</v>
-      </c>
       <c r="Q26" t="n">
-        <v>5.2</v>
+        <v>3.6</v>
       </c>
       <c r="R26" t="n">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="S26" t="n">
-        <v>2.43</v>
+        <v>2.25</v>
       </c>
       <c r="T26" t="n">
-        <v>3.48</v>
+        <v>3.75</v>
       </c>
       <c r="U26" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="V26" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="W26" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="X26" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AC26" t="n">
         <v>2.5</v>
       </c>
-      <c r="Y26" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Z26" t="n">
+      <c r="AD26" t="n">
         <v>1.5</v>
       </c>
-      <c r="AA26" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>1.63</v>
-      </c>
       <c r="AE26" t="inlineStr">
         <is>
-          <t>['65', '90+5']</t>
+          <t>['35']</t>
         </is>
       </c>
       <c r="AF26" t="inlineStr">
         <is>
-          <t>['16']</t>
+          <t>['8', '72']</t>
         </is>
       </c>
       <c r="AG26" t="n">
-        <v>1.18</v>
+        <v>1.37</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.92</v>
+        <v>1.45</v>
       </c>
       <c r="AI26" t="n">
-        <v>1.63</v>
+        <v>2.38</v>
       </c>
       <c r="AJ26" t="n">
-        <v>2.94</v>
+        <v>2</v>
       </c>
       <c r="AK26" s="3" t="n">
         <v>45646.625</v>
@@ -3858,7 +3858,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3868,16 +3868,16 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Ingolstadt</t>
+          <t>Leixões</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>CD Mafra</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H27" t="n">
         <v>1</v>
@@ -3894,83 +3894,83 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.15</v>
+        <v>1.8</v>
       </c>
       <c r="M27" t="n">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="N27" t="n">
-        <v>2.7</v>
+        <v>4.2</v>
       </c>
       <c r="O27" t="n">
-        <v>2.62</v>
+        <v>2.47</v>
       </c>
       <c r="P27" t="n">
-        <v>2.4</v>
+        <v>1.97</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.12</v>
+        <v>5.2</v>
       </c>
       <c r="R27" t="n">
-        <v>1.23</v>
+        <v>1.52</v>
       </c>
       <c r="S27" t="n">
-        <v>3.9</v>
+        <v>2.43</v>
       </c>
       <c r="T27" t="n">
-        <v>2.11</v>
+        <v>3.48</v>
       </c>
       <c r="U27" t="n">
-        <v>1.68</v>
+        <v>1.28</v>
       </c>
       <c r="V27" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="W27" t="n">
-        <v>1.08</v>
+        <v>1.42</v>
       </c>
       <c r="X27" t="n">
-        <v>5.45</v>
+        <v>2.5</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.44</v>
+        <v>2.3</v>
       </c>
       <c r="Z27" t="n">
-        <v>2.6</v>
+        <v>1.5</v>
       </c>
       <c r="AA27" t="n">
-        <v>2.15</v>
+        <v>4.33</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.6</v>
+        <v>1.15</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.38</v>
+        <v>2.14</v>
       </c>
       <c r="AD27" t="n">
-        <v>2.71</v>
+        <v>1.63</v>
       </c>
       <c r="AE27" t="inlineStr">
         <is>
-          <t>['59']</t>
+          <t>['65', '90+5']</t>
         </is>
       </c>
       <c r="AF27" t="inlineStr">
         <is>
-          <t>['23']</t>
+          <t>['16']</t>
         </is>
       </c>
       <c r="AG27" t="n">
-        <v>1.4</v>
+        <v>1.18</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.59</v>
+        <v>1.92</v>
       </c>
       <c r="AI27" t="n">
-        <v>1.78</v>
+        <v>1.63</v>
       </c>
       <c r="AJ27" t="n">
-        <v>1.97</v>
+        <v>2.94</v>
       </c>
       <c r="AK27" s="3" t="n">
         <v>45646.625</v>
@@ -3987,7 +3987,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,22 +3997,22 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Ingolstadt</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="G28" t="n">
         <v>1</v>
       </c>
       <c r="H28" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J28" t="n">
         <v>1</v>
@@ -4023,83 +4023,83 @@
         </is>
       </c>
       <c r="L28" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="M28" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="N28" t="n">
         <v>2.7</v>
       </c>
-      <c r="M28" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="N28" t="n">
-        <v>2.55</v>
-      </c>
       <c r="O28" t="n">
-        <v>3.75</v>
+        <v>2.62</v>
       </c>
       <c r="P28" t="n">
-        <v>1.8</v>
+        <v>2.4</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.6</v>
+        <v>3.12</v>
       </c>
       <c r="R28" t="n">
-        <v>1.57</v>
+        <v>1.23</v>
       </c>
       <c r="S28" t="n">
-        <v>2.25</v>
+        <v>3.9</v>
       </c>
       <c r="T28" t="n">
-        <v>3.75</v>
+        <v>2.11</v>
       </c>
       <c r="U28" t="n">
-        <v>1.25</v>
+        <v>1.68</v>
       </c>
       <c r="V28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W28" t="n">
         <v>1.08</v>
       </c>
-      <c r="W28" t="n">
-        <v>1.43</v>
-      </c>
       <c r="X28" t="n">
-        <v>2.7</v>
+        <v>5.45</v>
       </c>
       <c r="Y28" t="n">
-        <v>3</v>
+        <v>1.44</v>
       </c>
       <c r="Z28" t="n">
-        <v>1.36</v>
+        <v>2.6</v>
       </c>
       <c r="AA28" t="n">
-        <v>4.3</v>
+        <v>2.15</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.19</v>
+        <v>1.6</v>
       </c>
       <c r="AC28" t="n">
-        <v>2.5</v>
+        <v>1.38</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.5</v>
+        <v>2.71</v>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
-          <t>['35']</t>
+          <t>['59']</t>
         </is>
       </c>
       <c r="AF28" t="inlineStr">
         <is>
-          <t>['8', '72']</t>
+          <t>['23']</t>
         </is>
       </c>
       <c r="AG28" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.45</v>
+        <v>1.59</v>
       </c>
       <c r="AI28" t="n">
-        <v>2.38</v>
+        <v>1.78</v>
       </c>
       <c r="AJ28" t="n">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="AK28" s="3" t="n">
         <v>45646.625</v>
@@ -4116,7 +4116,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4126,22 +4126,22 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Club Brugge II</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Zulte-Waregem</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H29" t="n">
         <v>3</v>
       </c>
       <c r="I29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J29" t="n">
         <v>1</v>
@@ -4152,83 +4152,83 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.71</v>
+        <v>3.8</v>
       </c>
       <c r="M29" t="n">
-        <v>4.34</v>
+        <v>3.6</v>
       </c>
       <c r="N29" t="n">
-        <v>4.08</v>
+        <v>1.73</v>
       </c>
       <c r="O29" t="n">
-        <v>2.25</v>
+        <v>4</v>
       </c>
       <c r="P29" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="R29" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="S29" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="T29" t="n">
         <v>2.5</v>
       </c>
-      <c r="Q29" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="R29" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S29" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="T29" t="n">
-        <v>2.2</v>
-      </c>
       <c r="U29" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="V29" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W29" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="X29" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AE29" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF29" t="inlineStr">
+        <is>
+          <t>['3', '72', '90+2']</t>
+        </is>
+      </c>
+      <c r="AG29" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AJ29" t="n">
         <v>1.62</v>
-      </c>
-      <c r="V29" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W29" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="X29" t="n">
-        <v>5</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="Z29" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AE29" t="inlineStr">
-        <is>
-          <t>['45+2', '77', '88']</t>
-        </is>
-      </c>
-      <c r="AF29" t="inlineStr">
-        <is>
-          <t>['16', '60', '79']</t>
-        </is>
-      </c>
-      <c r="AG29" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AH29" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AI29" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AJ29" t="n">
-        <v>2.63</v>
       </c>
       <c r="AK29" s="3" t="n">
         <v>45646.66666666666</v>
@@ -4245,7 +4245,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4255,16 +4255,16 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>PEC Zwolle</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H30" t="n">
         <v>1</v>
@@ -4281,19 +4281,19 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="M30" t="n">
-        <v>3.46</v>
+        <v>3.6</v>
       </c>
       <c r="N30" t="n">
-        <v>2.31</v>
+        <v>2.37</v>
       </c>
       <c r="O30" t="n">
         <v>3.4</v>
       </c>
       <c r="P30" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="Q30" t="n">
         <v>2.88</v>
@@ -4305,31 +4305,31 @@
         <v>3.25</v>
       </c>
       <c r="T30" t="n">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="U30" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="V30" t="n">
         <v>1.03</v>
       </c>
       <c r="W30" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="X30" t="n">
-        <v>4</v>
+        <v>4.25</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="Z30" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AA30" t="n">
-        <v>2.9</v>
+        <v>2.75</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="AC30" t="n">
         <v>1.62</v>
@@ -4339,22 +4339,22 @@
       </c>
       <c r="AE30" t="inlineStr">
         <is>
-          <t>['38', '54', '68']</t>
+          <t>['10']</t>
         </is>
       </c>
       <c r="AF30" t="inlineStr">
         <is>
-          <t>['33']</t>
+          <t>['41']</t>
         </is>
       </c>
       <c r="AG30" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AI30" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AJ30" t="n">
         <v>1.73</v>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4384,23 +4384,23 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Club Brugge II</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Zulte-Waregem</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H31" t="n">
+        <v>4</v>
+      </c>
+      <c r="I31" t="n">
         <v>3</v>
       </c>
-      <c r="I31" t="n">
-        <v>0</v>
-      </c>
       <c r="J31" t="n">
         <v>1</v>
       </c>
@@ -4410,83 +4410,83 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>3.8</v>
+        <v>2.55</v>
       </c>
       <c r="M31" t="n">
-        <v>3.6</v>
+        <v>3.83</v>
       </c>
       <c r="N31" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="O31" t="n">
+        <v>3</v>
+      </c>
+      <c r="P31" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="R31" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S31" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="V31" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W31" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="X31" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AE31" t="inlineStr">
+        <is>
+          <t>['7', '38', '44', '66', '78', '81']</t>
+        </is>
+      </c>
+      <c r="AF31" t="inlineStr">
+        <is>
+          <t>['21', '46', '68', '83']</t>
+        </is>
+      </c>
+      <c r="AG31" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AI31" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ31" t="n">
         <v>1.73</v>
-      </c>
-      <c r="O31" t="n">
-        <v>4</v>
-      </c>
-      <c r="P31" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="R31" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="S31" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="T31" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="U31" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="V31" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W31" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="X31" t="n">
-        <v>4</v>
-      </c>
-      <c r="Y31" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="Z31" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AA31" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AD31" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AE31" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF31" t="inlineStr">
-        <is>
-          <t>['3', '72', '90+2']</t>
-        </is>
-      </c>
-      <c r="AG31" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AH31" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AI31" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AJ31" t="n">
-        <v>1.62</v>
       </c>
       <c r="AK31" s="3" t="n">
         <v>45646.66666666666</v>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4513,25 +4513,25 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Francs Borains</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>KRC Genk II</t>
         </is>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H32" t="n">
         <v>2</v>
       </c>
       <c r="I32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J32" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K32" t="inlineStr">
         <is>
@@ -4539,83 +4539,83 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.4</v>
+        <v>1.67</v>
       </c>
       <c r="M32" t="n">
-        <v>5.15</v>
+        <v>3.8</v>
       </c>
       <c r="N32" t="n">
-        <v>6.57</v>
+        <v>3.8</v>
       </c>
       <c r="O32" t="n">
-        <v>1.91</v>
+        <v>2.22</v>
       </c>
       <c r="P32" t="n">
-        <v>2.75</v>
+        <v>2.35</v>
       </c>
       <c r="Q32" t="n">
-        <v>5.5</v>
+        <v>4.15</v>
       </c>
       <c r="R32" t="n">
-        <v>1.2</v>
+        <v>1.26</v>
       </c>
       <c r="S32" t="n">
-        <v>4.33</v>
+        <v>3.62</v>
       </c>
       <c r="T32" t="n">
-        <v>2</v>
+        <v>2.27</v>
       </c>
       <c r="U32" t="n">
-        <v>1.73</v>
+        <v>1.59</v>
       </c>
       <c r="V32" t="n">
         <v>1.01</v>
       </c>
       <c r="W32" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X32" t="n">
-        <v>6.5</v>
+        <v>4.85</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.36</v>
+        <v>1.53</v>
       </c>
       <c r="Z32" t="n">
-        <v>3.1</v>
+        <v>2.35</v>
       </c>
       <c r="AA32" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AE32" t="inlineStr">
+        <is>
+          <t>['11', '75']</t>
+        </is>
+      </c>
+      <c r="AF32" t="inlineStr">
+        <is>
+          <t>['8', '31']</t>
+        </is>
+      </c>
+      <c r="AG32" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AH32" t="n">
         <v>1.97</v>
       </c>
-      <c r="AB32" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AC32" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AD32" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AE32" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF32" t="inlineStr">
-        <is>
-          <t>['82', '90+1']</t>
-        </is>
-      </c>
-      <c r="AG32" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AH32" t="n">
-        <v>2.85</v>
-      </c>
       <c r="AI32" t="n">
-        <v>1.33</v>
+        <v>1.54</v>
       </c>
       <c r="AJ32" t="n">
-        <v>3.25</v>
+        <v>2.42</v>
       </c>
       <c r="AK32" s="3" t="n">
         <v>45646.66666666666</v>
@@ -4642,48 +4642,48 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G33" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H33" t="n">
+        <v>1</v>
+      </c>
+      <c r="I33" t="n">
+        <v>1</v>
+      </c>
+      <c r="J33" t="n">
+        <v>1</v>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L33" t="n">
         <v>3</v>
       </c>
-      <c r="I33" t="n">
-        <v>0</v>
-      </c>
-      <c r="J33" t="n">
-        <v>2</v>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L33" t="n">
-        <v>1.7</v>
-      </c>
       <c r="M33" t="n">
-        <v>3.97</v>
+        <v>3.46</v>
       </c>
       <c r="N33" t="n">
-        <v>4.56</v>
+        <v>2.31</v>
       </c>
       <c r="O33" t="n">
-        <v>2.3</v>
+        <v>3.4</v>
       </c>
       <c r="P33" t="n">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="Q33" t="n">
-        <v>4.5</v>
+        <v>2.88</v>
       </c>
       <c r="R33" t="n">
         <v>1.33</v>
@@ -4692,59 +4692,59 @@
         <v>3.25</v>
       </c>
       <c r="T33" t="n">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="U33" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="V33" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="W33" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="X33" t="n">
-        <v>4.33</v>
+        <v>4</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="Z33" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AD33" t="n">
         <v>2.2</v>
       </c>
-      <c r="AA33" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AB33" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AC33" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AD33" t="n">
-        <v>2.1</v>
-      </c>
       <c r="AE33" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['38', '54', '68']</t>
         </is>
       </c>
       <c r="AF33" t="inlineStr">
         <is>
-          <t>['16', '21', '56']</t>
+          <t>['33']</t>
         </is>
       </c>
       <c r="AG33" t="n">
-        <v>1.22</v>
+        <v>1.62</v>
       </c>
       <c r="AH33" t="n">
-        <v>2.05</v>
+        <v>1.4</v>
       </c>
       <c r="AI33" t="n">
-        <v>1.5</v>
+        <v>2.2</v>
       </c>
       <c r="AJ33" t="n">
-        <v>2.75</v>
+        <v>1.73</v>
       </c>
       <c r="AK33" s="3" t="n">
         <v>45646.66666666666</v>
@@ -4761,7 +4761,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4771,19 +4771,19 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>PEC Zwolle</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G34" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H34" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I34" t="n">
         <v>1</v>
@@ -4797,83 +4797,83 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.8</v>
+        <v>1.71</v>
       </c>
       <c r="M34" t="n">
-        <v>3.6</v>
+        <v>4.34</v>
       </c>
       <c r="N34" t="n">
-        <v>2.37</v>
+        <v>4.08</v>
       </c>
       <c r="O34" t="n">
-        <v>3.4</v>
+        <v>2.25</v>
       </c>
       <c r="P34" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="R34" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S34" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="T34" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="V34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W34" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="X34" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AA34" t="n">
         <v>2.3</v>
       </c>
-      <c r="Q34" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="R34" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S34" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="T34" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="U34" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="V34" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W34" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="X34" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="Y34" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="Z34" t="n">
+      <c r="AB34" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AE34" t="inlineStr">
+        <is>
+          <t>['45+2', '77', '88']</t>
+        </is>
+      </c>
+      <c r="AF34" t="inlineStr">
+        <is>
+          <t>['16', '60', '79']</t>
+        </is>
+      </c>
+      <c r="AG34" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AH34" t="n">
         <v>2.1</v>
       </c>
-      <c r="AA34" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AB34" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AC34" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AD34" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AE34" t="inlineStr">
-        <is>
-          <t>['10']</t>
-        </is>
-      </c>
-      <c r="AF34" t="inlineStr">
-        <is>
-          <t>['41']</t>
-        </is>
-      </c>
-      <c r="AG34" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AH34" t="n">
+      <c r="AI34" t="n">
         <v>1.44</v>
       </c>
-      <c r="AI34" t="n">
-        <v>2.1</v>
-      </c>
       <c r="AJ34" t="n">
-        <v>1.73</v>
+        <v>2.63</v>
       </c>
       <c r="AK34" s="3" t="n">
         <v>45646.66666666666</v>
@@ -4900,25 +4900,25 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G35" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I35" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K35" t="inlineStr">
         <is>
@@ -4926,83 +4926,83 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.55</v>
+        <v>1.4</v>
       </c>
       <c r="M35" t="n">
-        <v>3.83</v>
+        <v>5.15</v>
       </c>
       <c r="N35" t="n">
-        <v>2.48</v>
+        <v>6.57</v>
       </c>
       <c r="O35" t="n">
-        <v>3</v>
+        <v>1.91</v>
       </c>
       <c r="P35" t="n">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="Q35" t="n">
-        <v>2.88</v>
+        <v>5.5</v>
       </c>
       <c r="R35" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="S35" t="n">
-        <v>3.75</v>
+        <v>4.33</v>
       </c>
       <c r="T35" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="U35" t="n">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="V35" t="n">
         <v>1.01</v>
       </c>
       <c r="W35" t="n">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="X35" t="n">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="Z35" t="n">
-        <v>2.7</v>
+        <v>3.1</v>
       </c>
       <c r="AA35" t="n">
-        <v>2.1</v>
+        <v>1.97</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.72</v>
+        <v>1.85</v>
       </c>
       <c r="AC35" t="n">
-        <v>1.4</v>
+        <v>1.53</v>
       </c>
       <c r="AD35" t="n">
-        <v>2.75</v>
+        <v>2.38</v>
       </c>
       <c r="AE35" t="inlineStr">
         <is>
-          <t>['7', '38', '44', '66', '78', '81']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF35" t="inlineStr">
         <is>
-          <t>['21', '46', '68', '83']</t>
+          <t>['82', '90+1']</t>
         </is>
       </c>
       <c r="AG35" t="n">
-        <v>1.57</v>
+        <v>1.11</v>
       </c>
       <c r="AH35" t="n">
-        <v>1.52</v>
+        <v>2.85</v>
       </c>
       <c r="AI35" t="n">
-        <v>2</v>
+        <v>1.33</v>
       </c>
       <c r="AJ35" t="n">
-        <v>1.73</v>
+        <v>3.25</v>
       </c>
       <c r="AK35" s="3" t="n">
         <v>45646.66666666666</v>
@@ -5019,7 +5019,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5029,22 +5029,22 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Francs Borains</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>KRC Genk II</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G36" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J36" t="n">
         <v>2</v>
@@ -5055,83 +5055,83 @@
         </is>
       </c>
       <c r="L36" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="M36" t="n">
+        <v>3.97</v>
+      </c>
+      <c r="N36" t="n">
+        <v>4.56</v>
+      </c>
+      <c r="O36" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="P36" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="R36" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S36" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T36" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="U36" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V36" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W36" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="X36" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AC36" t="n">
         <v>1.67</v>
       </c>
-      <c r="M36" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="N36" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="O36" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="P36" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="Q36" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="R36" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="S36" t="n">
-        <v>3.62</v>
-      </c>
-      <c r="T36" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="U36" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="V36" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W36" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X36" t="n">
-        <v>4.85</v>
-      </c>
-      <c r="Y36" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="Z36" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AA36" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AB36" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AC36" t="n">
+      <c r="AD36" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AE36" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF36" t="inlineStr">
+        <is>
+          <t>['16', '21', '56']</t>
+        </is>
+      </c>
+      <c r="AG36" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AH36" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AI36" t="n">
         <v>1.5</v>
       </c>
-      <c r="AD36" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="AE36" t="inlineStr">
-        <is>
-          <t>['11', '75']</t>
-        </is>
-      </c>
-      <c r="AF36" t="inlineStr">
-        <is>
-          <t>['8', '31']</t>
-        </is>
-      </c>
-      <c r="AG36" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AH36" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="AI36" t="n">
-        <v>1.54</v>
-      </c>
       <c r="AJ36" t="n">
-        <v>2.42</v>
+        <v>2.75</v>
       </c>
       <c r="AK36" s="3" t="n">
         <v>45646.66666666666</v>
@@ -5148,7 +5148,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5158,22 +5158,22 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Turris Neapolis</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="G37" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -5184,43 +5184,43 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>1.17</v>
+        <v>4.2</v>
       </c>
       <c r="M37" t="n">
-        <v>6</v>
+        <v>3.6</v>
       </c>
       <c r="N37" t="n">
-        <v>15</v>
+        <v>1.7</v>
       </c>
       <c r="O37" t="n">
-        <v>1.62</v>
+        <v>4.75</v>
       </c>
       <c r="P37" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="Q37" t="n">
-        <v>13</v>
+        <v>2.3</v>
       </c>
       <c r="R37" t="n">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="S37" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="T37" t="n">
-        <v>2.63</v>
+        <v>3.4</v>
       </c>
       <c r="U37" t="n">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="V37" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="W37" t="n">
-        <v>1.2</v>
+        <v>1.37</v>
       </c>
       <c r="X37" t="n">
-        <v>4</v>
+        <v>2.95</v>
       </c>
       <c r="Y37" t="n">
         <v>1.85</v>
@@ -5229,38 +5229,38 @@
         <v>1.95</v>
       </c>
       <c r="AA37" t="n">
-        <v>2.25</v>
+        <v>3.85</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.55</v>
+        <v>1.24</v>
       </c>
       <c r="AC37" t="n">
-        <v>2.63</v>
+        <v>1.83</v>
       </c>
       <c r="AD37" t="n">
-        <v>1.44</v>
+        <v>1.83</v>
       </c>
       <c r="AE37" t="inlineStr">
         <is>
-          <t>['6', '66', '84']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF37" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['85']</t>
         </is>
       </c>
       <c r="AG37" t="n">
-        <v>1.03</v>
+        <v>1.58</v>
       </c>
       <c r="AH37" t="n">
-        <v>3.55</v>
+        <v>1.27</v>
       </c>
       <c r="AI37" t="n">
-        <v>1.13</v>
+        <v>2.88</v>
       </c>
       <c r="AJ37" t="n">
-        <v>7.5</v>
+        <v>1.5</v>
       </c>
       <c r="AK37" s="3" t="n">
         <v>45646.6875</v>
@@ -5277,7 +5277,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5287,25 +5287,25 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Brescia</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="G38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H38" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I38" t="n">
         <v>0</v>
       </c>
       <c r="J38" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K38" t="inlineStr">
         <is>
@@ -5313,83 +5313,83 @@
         </is>
       </c>
       <c r="L38" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="M38" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="N38" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="O38" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="P38" t="n">
         <v>2.05</v>
       </c>
-      <c r="M38" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="N38" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="O38" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="P38" t="n">
-        <v>2</v>
-      </c>
       <c r="Q38" t="n">
-        <v>3.95</v>
+        <v>2.5</v>
       </c>
       <c r="R38" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="S38" t="n">
-        <v>2.65</v>
+        <v>2.63</v>
       </c>
       <c r="T38" t="n">
-        <v>2.9</v>
+        <v>3.25</v>
       </c>
       <c r="U38" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="V38" t="n">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="W38" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="X38" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="Z38" t="n">
         <v>1.7</v>
       </c>
       <c r="AA38" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AC38" t="n">
-        <v>1.77</v>
+        <v>2</v>
       </c>
       <c r="AD38" t="n">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="AE38" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['66']</t>
         </is>
       </c>
       <c r="AF38" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['5', '17']</t>
         </is>
       </c>
       <c r="AG38" t="n">
-        <v>1.28</v>
+        <v>1.62</v>
       </c>
       <c r="AH38" t="n">
-        <v>1.7</v>
+        <v>1.27</v>
       </c>
       <c r="AI38" t="n">
-        <v>1.8</v>
+        <v>2.88</v>
       </c>
       <c r="AJ38" t="n">
-        <v>2.38</v>
+        <v>1.57</v>
       </c>
       <c r="AK38" s="3" t="n">
         <v>45646.6875</v>
@@ -5416,25 +5416,25 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Turris Neapolis</t>
         </is>
       </c>
       <c r="G39" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H39" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J39" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K39" t="inlineStr">
         <is>
@@ -5442,83 +5442,83 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>4.2</v>
+        <v>1.17</v>
       </c>
       <c r="M39" t="n">
-        <v>3.2</v>
+        <v>6</v>
       </c>
       <c r="N39" t="n">
-        <v>1.83</v>
+        <v>15</v>
       </c>
       <c r="O39" t="n">
-        <v>4.5</v>
+        <v>1.62</v>
       </c>
       <c r="P39" t="n">
-        <v>2.05</v>
+        <v>2.4</v>
       </c>
       <c r="Q39" t="n">
-        <v>2.5</v>
+        <v>13</v>
       </c>
       <c r="R39" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S39" t="n">
+        <v>3</v>
+      </c>
+      <c r="T39" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="U39" t="n">
         <v>1.44</v>
       </c>
-      <c r="S39" t="n">
+      <c r="V39" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W39" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="X39" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AC39" t="n">
         <v>2.63</v>
       </c>
-      <c r="T39" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="U39" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V39" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W39" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="X39" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="Y39" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Z39" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AA39" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AB39" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AC39" t="n">
-        <v>2</v>
-      </c>
       <c r="AD39" t="n">
-        <v>1.73</v>
+        <v>1.44</v>
       </c>
       <c r="AE39" t="inlineStr">
         <is>
-          <t>['66']</t>
+          <t>['6', '66', '84']</t>
         </is>
       </c>
       <c r="AF39" t="inlineStr">
         <is>
-          <t>['5', '17']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG39" t="n">
-        <v>1.62</v>
+        <v>1.03</v>
       </c>
       <c r="AH39" t="n">
-        <v>1.27</v>
+        <v>3.55</v>
       </c>
       <c r="AI39" t="n">
-        <v>2.88</v>
+        <v>1.13</v>
       </c>
       <c r="AJ39" t="n">
-        <v>1.57</v>
+        <v>7.5</v>
       </c>
       <c r="AK39" s="3" t="n">
         <v>45646.6875</v>
@@ -5535,7 +5535,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5545,16 +5545,16 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>FC Cartagena</t>
+          <t>Real Betis II</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>Sevilla II</t>
         </is>
       </c>
       <c r="G40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H40" t="n">
         <v>0</v>
@@ -5571,83 +5571,83 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>3.2</v>
+        <v>1.84</v>
       </c>
       <c r="M40" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="N40" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="O40" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="P40" t="n">
         <v>2.1</v>
       </c>
-      <c r="O40" t="n">
-        <v>4</v>
-      </c>
-      <c r="P40" t="n">
-        <v>2.05</v>
-      </c>
       <c r="Q40" t="n">
-        <v>2.88</v>
+        <v>4.75</v>
       </c>
       <c r="R40" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="S40" t="n">
-        <v>2.63</v>
+        <v>2.75</v>
       </c>
       <c r="T40" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U40" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V40" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W40" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="X40" t="n">
         <v>3.25</v>
       </c>
-      <c r="U40" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V40" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="W40" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="X40" t="n">
+      <c r="Y40" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AE40" t="inlineStr">
+        <is>
+          <t>['85']</t>
+        </is>
+      </c>
+      <c r="AF40" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG40" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AH40" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AI40" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AJ40" t="n">
         <v>3</v>
-      </c>
-      <c r="Y40" t="n">
-        <v>2</v>
-      </c>
-      <c r="Z40" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AA40" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AB40" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AC40" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AD40" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AE40" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF40" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG40" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AH40" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AI40" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AJ40" t="n">
-        <v>1.73</v>
       </c>
       <c r="AK40" s="3" t="n">
         <v>45646.6875</v>
@@ -5664,7 +5664,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5674,25 +5674,25 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>FC Cartagena</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>SPAL</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="G41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K41" t="inlineStr">
         <is>
@@ -5700,83 +5700,83 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>1.65</v>
+        <v>3.2</v>
       </c>
       <c r="M41" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="N41" t="n">
-        <v>4.75</v>
+        <v>2.1</v>
       </c>
       <c r="O41" t="n">
-        <v>2.3</v>
+        <v>4</v>
       </c>
       <c r="P41" t="n">
         <v>2.05</v>
       </c>
       <c r="Q41" t="n">
-        <v>5.5</v>
+        <v>2.88</v>
       </c>
       <c r="R41" t="n">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="S41" t="n">
-        <v>2.38</v>
+        <v>2.63</v>
       </c>
       <c r="T41" t="n">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="U41" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="V41" t="n">
         <v>1.07</v>
       </c>
       <c r="W41" t="n">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="X41" t="n">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="Y41" t="n">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="Z41" t="n">
         <v>1.67</v>
       </c>
       <c r="AA41" t="n">
-        <v>4.2</v>
+        <v>3.75</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AC41" t="n">
-        <v>2.1</v>
+        <v>1.83</v>
       </c>
       <c r="AD41" t="n">
-        <v>1.67</v>
+        <v>1.83</v>
       </c>
       <c r="AE41" t="inlineStr">
         <is>
-          <t>['9']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF41" t="inlineStr">
         <is>
-          <t>['17']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG41" t="n">
-        <v>1.22</v>
+        <v>1.66</v>
       </c>
       <c r="AH41" t="n">
-        <v>1.66</v>
+        <v>1.33</v>
       </c>
       <c r="AI41" t="n">
-        <v>1.44</v>
+        <v>2.4</v>
       </c>
       <c r="AJ41" t="n">
-        <v>3.2</v>
+        <v>1.73</v>
       </c>
       <c r="AK41" s="3" t="n">
         <v>45646.6875</v>
@@ -5793,7 +5793,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5803,19 +5803,19 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>SD Ponferradina</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>SD Tarazona</t>
         </is>
       </c>
       <c r="G42" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I42" t="n">
         <v>0</v>
@@ -5829,83 +5829,83 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>4.2</v>
+        <v>1.6</v>
       </c>
       <c r="M42" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="N42" t="n">
+        <v>5</v>
+      </c>
+      <c r="O42" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="P42" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>6</v>
+      </c>
+      <c r="R42" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S42" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="T42" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="U42" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V42" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W42" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="X42" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AB42" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AE42" t="inlineStr">
+        <is>
+          <t>['71', '73']</t>
+        </is>
+      </c>
+      <c r="AF42" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG42" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AH42" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AI42" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AJ42" t="n">
         <v>3.6</v>
-      </c>
-      <c r="N42" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="O42" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="P42" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q42" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="R42" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="S42" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="T42" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="U42" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="V42" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W42" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="X42" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="Y42" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="Z42" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AA42" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AB42" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AC42" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AD42" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AE42" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF42" t="inlineStr">
-        <is>
-          <t>['85']</t>
-        </is>
-      </c>
-      <c r="AG42" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AH42" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AI42" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AJ42" t="n">
-        <v>1.5</v>
       </c>
       <c r="AK42" s="3" t="n">
         <v>45646.6875</v>
@@ -5922,7 +5922,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5932,109 +5932,109 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Pontedera</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>RB Leipzig</t>
+          <t>Legnago Salus</t>
         </is>
       </c>
       <c r="G43" t="n">
+        <v>0</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0</v>
+      </c>
+      <c r="I43" t="n">
+        <v>0</v>
+      </c>
+      <c r="J43" t="n">
+        <v>0</v>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L43" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="M43" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N43" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O43" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="P43" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q43" t="n">
         <v>5</v>
       </c>
-      <c r="H43" t="n">
-        <v>1</v>
-      </c>
-      <c r="I43" t="n">
+      <c r="R43" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S43" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="T43" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="U43" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V43" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W43" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="X43" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AB43" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AD43" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AE43" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF43" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG43" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AH43" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AI43" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AJ43" t="n">
         <v>3</v>
-      </c>
-      <c r="J43" t="n">
-        <v>1</v>
-      </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L43" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="M43" t="n">
-        <v>5</v>
-      </c>
-      <c r="N43" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="O43" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="P43" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="Q43" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="R43" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="S43" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="T43" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="U43" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="V43" t="n">
-        <v>0</v>
-      </c>
-      <c r="W43" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="X43" t="n">
-        <v>7</v>
-      </c>
-      <c r="Y43" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="Z43" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AA43" t="n">
-        <v>2</v>
-      </c>
-      <c r="AB43" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AC43" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AD43" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AE43" t="inlineStr">
-        <is>
-          <t>['1', '25', '36', '75', '78']</t>
-        </is>
-      </c>
-      <c r="AF43" t="inlineStr">
-        <is>
-          <t>['2']</t>
-        </is>
-      </c>
-      <c r="AG43" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AH43" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AI43" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AJ43" t="n">
-        <v>3.75</v>
       </c>
       <c r="AK43" s="3" t="n">
         <v>45646.6875</v>
@@ -6051,7 +6051,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -6061,25 +6061,25 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>SD Ponferradina</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>SD Tarazona</t>
+          <t>SPAL</t>
         </is>
       </c>
       <c r="G44" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K44" t="inlineStr">
         <is>
@@ -6087,83 +6087,83 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="M44" t="n">
-        <v>3.9</v>
+        <v>3.4</v>
       </c>
       <c r="N44" t="n">
-        <v>5</v>
+        <v>4.75</v>
       </c>
       <c r="O44" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="P44" t="n">
         <v>2.05</v>
       </c>
       <c r="Q44" t="n">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="R44" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="S44" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="T44" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="U44" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="V44" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="W44" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="X44" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="Y44" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Z44" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AA44" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AB44" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AC44" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AD44" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AE44" t="inlineStr">
+        <is>
+          <t>['9']</t>
+        </is>
+      </c>
+      <c r="AF44" t="inlineStr">
+        <is>
+          <t>['17']</t>
+        </is>
+      </c>
+      <c r="AG44" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AH44" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AI44" t="n">
         <v>1.44</v>
       </c>
-      <c r="S44" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="T44" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="U44" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V44" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W44" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="X44" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y44" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="Z44" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AA44" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AB44" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AC44" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AD44" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AE44" t="inlineStr">
-        <is>
-          <t>['71', '73']</t>
-        </is>
-      </c>
-      <c r="AF44" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG44" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AH44" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AI44" t="n">
-        <v>1.4</v>
-      </c>
       <c r="AJ44" t="n">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="AK44" s="3" t="n">
         <v>45646.6875</v>
@@ -6190,25 +6190,25 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Pontedera</t>
+          <t>Lucchese</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Legnago Salus</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="G45" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H45" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I45" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K45" t="inlineStr">
         <is>
@@ -6216,83 +6216,83 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>1.67</v>
+        <v>2.1</v>
       </c>
       <c r="M45" t="n">
-        <v>3.4</v>
+        <v>2.9</v>
       </c>
       <c r="N45" t="n">
-        <v>4.5</v>
+        <v>3.6</v>
       </c>
       <c r="O45" t="n">
-        <v>2.3</v>
+        <v>2.88</v>
       </c>
       <c r="P45" t="n">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="Q45" t="n">
-        <v>5</v>
+        <v>4.33</v>
       </c>
       <c r="R45" t="n">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="S45" t="n">
-        <v>2.63</v>
+        <v>2.38</v>
       </c>
       <c r="T45" t="n">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="U45" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="V45" t="n">
         <v>1.04</v>
       </c>
       <c r="W45" t="n">
-        <v>1.33</v>
+        <v>1.52</v>
       </c>
       <c r="X45" t="n">
-        <v>3.15</v>
+        <v>2.38</v>
       </c>
       <c r="Y45" t="n">
-        <v>2</v>
+        <v>2.38</v>
       </c>
       <c r="Z45" t="n">
-        <v>1.8</v>
+        <v>1.53</v>
       </c>
       <c r="AA45" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.27</v>
+        <v>1.18</v>
       </c>
       <c r="AC45" t="n">
-        <v>1.91</v>
+        <v>2.1</v>
       </c>
       <c r="AD45" t="n">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="AE45" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['22', '24', '27']</t>
         </is>
       </c>
       <c r="AF45" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['14', '62', '83']</t>
         </is>
       </c>
       <c r="AG45" t="n">
-        <v>1.19</v>
+        <v>1.29</v>
       </c>
       <c r="AH45" t="n">
-        <v>1.81</v>
+        <v>1.51</v>
       </c>
       <c r="AI45" t="n">
-        <v>1.5</v>
+        <v>1.73</v>
       </c>
       <c r="AJ45" t="n">
-        <v>3</v>
+        <v>2.63</v>
       </c>
       <c r="AK45" s="3" t="n">
         <v>45646.6875</v>
@@ -6309,7 +6309,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -6319,19 +6319,19 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Lucchese</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>RB Leipzig</t>
         </is>
       </c>
       <c r="G46" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H46" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I46" t="n">
         <v>3</v>
@@ -6345,83 +6345,83 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>2.1</v>
+        <v>1.5</v>
       </c>
       <c r="M46" t="n">
-        <v>2.9</v>
+        <v>5</v>
       </c>
       <c r="N46" t="n">
-        <v>3.6</v>
+        <v>5.25</v>
       </c>
       <c r="O46" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="P46" t="n">
         <v>2.88</v>
       </c>
-      <c r="P46" t="n">
+      <c r="Q46" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="R46" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="S46" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="T46" t="n">
         <v>1.91</v>
       </c>
-      <c r="Q46" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="R46" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="S46" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="T46" t="n">
+      <c r="U46" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="V46" t="n">
+        <v>0</v>
+      </c>
+      <c r="W46" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X46" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y46" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Z46" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AA46" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB46" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AC46" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AD46" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AE46" t="inlineStr">
+        <is>
+          <t>['1', '25', '36', '75', '78']</t>
+        </is>
+      </c>
+      <c r="AF46" t="inlineStr">
+        <is>
+          <t>['2']</t>
+        </is>
+      </c>
+      <c r="AG46" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AH46" t="n">
         <v>3.5</v>
       </c>
-      <c r="U46" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="V46" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W46" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="X46" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="Y46" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="Z46" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AA46" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AB46" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AC46" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AD46" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AE46" t="inlineStr">
-        <is>
-          <t>['22', '24', '27']</t>
-        </is>
-      </c>
-      <c r="AF46" t="inlineStr">
-        <is>
-          <t>['14', '62', '83']</t>
-        </is>
-      </c>
-      <c r="AG46" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AH46" t="n">
-        <v>1.51</v>
-      </c>
       <c r="AI46" t="n">
-        <v>1.73</v>
+        <v>1.25</v>
       </c>
       <c r="AJ46" t="n">
-        <v>2.63</v>
+        <v>3.75</v>
       </c>
       <c r="AK46" s="3" t="n">
         <v>45646.6875</v>
@@ -6438,7 +6438,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -6448,16 +6448,16 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Real Betis II</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Sevilla II</t>
+          <t>Brescia</t>
         </is>
       </c>
       <c r="G47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H47" t="n">
         <v>0</v>
@@ -6474,83 +6474,83 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>1.84</v>
+        <v>2.05</v>
       </c>
       <c r="M47" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="N47" t="n">
-        <v>4.3</v>
+        <v>3.2</v>
       </c>
       <c r="O47" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="P47" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="R47" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="S47" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="T47" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="U47" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V47" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="W47" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="X47" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="Y47" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Z47" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AA47" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AB47" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AC47" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AD47" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AE47" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF47" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG47" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AH47" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AI47" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AJ47" t="n">
         <v>2.38</v>
-      </c>
-      <c r="P47" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Q47" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="R47" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S47" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="T47" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U47" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V47" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W47" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="X47" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="Y47" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="Z47" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AA47" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AB47" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AC47" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AD47" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AE47" t="inlineStr">
-        <is>
-          <t>['85']</t>
-        </is>
-      </c>
-      <c r="AF47" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG47" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AH47" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AI47" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AJ47" t="n">
-        <v>3</v>
       </c>
       <c r="AK47" s="3" t="n">
         <v>45646.6875</v>
@@ -6567,7 +6567,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6577,22 +6577,22 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>KVC Westerlo</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>KV Mechelen</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="G48" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H48" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J48" t="n">
         <v>1</v>
@@ -6603,83 +6603,83 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="M48" t="n">
-        <v>3.9</v>
+        <v>3.4</v>
       </c>
       <c r="N48" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="O48" t="n">
-        <v>2.7</v>
+        <v>2.88</v>
       </c>
       <c r="P48" t="n">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="Q48" t="n">
-        <v>3.3</v>
+        <v>4</v>
       </c>
       <c r="R48" t="n">
-        <v>1.28</v>
+        <v>1.44</v>
       </c>
       <c r="S48" t="n">
-        <v>3.35</v>
+        <v>2.63</v>
       </c>
       <c r="T48" t="n">
-        <v>2.2</v>
+        <v>3.4</v>
       </c>
       <c r="U48" t="n">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="V48" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="W48" t="n">
-        <v>1.17</v>
+        <v>1.38</v>
       </c>
       <c r="X48" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="Y48" t="n">
-        <v>1.5</v>
+        <v>2.15</v>
       </c>
       <c r="Z48" t="n">
-        <v>2.4</v>
+        <v>1.65</v>
       </c>
       <c r="AA48" t="n">
-        <v>2.05</v>
+        <v>4.2</v>
       </c>
       <c r="AB48" t="n">
-        <v>1.7</v>
+        <v>1.22</v>
       </c>
       <c r="AC48" t="n">
-        <v>1.42</v>
+        <v>1.91</v>
       </c>
       <c r="AD48" t="n">
-        <v>2.6</v>
+        <v>1.8</v>
       </c>
       <c r="AE48" t="inlineStr">
         <is>
-          <t>['75']</t>
+          <t>['24', '68']</t>
         </is>
       </c>
       <c r="AF48" t="inlineStr">
         <is>
-          <t>['35']</t>
+          <t>['36', '60']</t>
         </is>
       </c>
       <c r="AG48" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AH48" t="n">
         <v>1.65</v>
       </c>
       <c r="AI48" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AJ48" t="n">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="AK48" s="3" t="n">
         <v>45646.69791666666</v>
@@ -6696,7 +6696,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6706,19 +6706,19 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="G49" t="n">
         <v>2</v>
       </c>
       <c r="H49" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I49" t="n">
         <v>1</v>
@@ -6732,83 +6732,83 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>2.15</v>
+        <v>1.8</v>
       </c>
       <c r="M49" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="N49" t="n">
+        <v>4</v>
+      </c>
+      <c r="O49" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="P49" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="R49" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S49" t="n">
         <v>3.4</v>
       </c>
-      <c r="N49" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="O49" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="P49" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="Q49" t="n">
-        <v>4</v>
-      </c>
-      <c r="R49" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S49" t="n">
-        <v>2.63</v>
-      </c>
       <c r="T49" t="n">
-        <v>3.4</v>
+        <v>2.38</v>
       </c>
       <c r="U49" t="n">
-        <v>1.3</v>
+        <v>1.53</v>
       </c>
       <c r="V49" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="W49" t="n">
-        <v>1.38</v>
+        <v>1.2</v>
       </c>
       <c r="X49" t="n">
-        <v>3</v>
+        <v>4.33</v>
       </c>
       <c r="Y49" t="n">
-        <v>2.15</v>
+        <v>1.61</v>
       </c>
       <c r="Z49" t="n">
-        <v>1.65</v>
+        <v>2.2</v>
       </c>
       <c r="AA49" t="n">
-        <v>4.2</v>
+        <v>2.55</v>
       </c>
       <c r="AB49" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AC49" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AD49" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AE49" t="inlineStr">
+        <is>
+          <t>['11', '75']</t>
+        </is>
+      </c>
+      <c r="AF49" t="inlineStr">
+        <is>
+          <t>['34']</t>
+        </is>
+      </c>
+      <c r="AG49" t="n">
         <v>1.22</v>
       </c>
-      <c r="AC49" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AD49" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AE49" t="inlineStr">
-        <is>
-          <t>['24', '68']</t>
-        </is>
-      </c>
-      <c r="AF49" t="inlineStr">
-        <is>
-          <t>['36', '60']</t>
-        </is>
-      </c>
-      <c r="AG49" t="n">
-        <v>1.33</v>
-      </c>
       <c r="AH49" t="n">
-        <v>1.65</v>
+        <v>1.95</v>
       </c>
       <c r="AI49" t="n">
-        <v>1.85</v>
+        <v>1.5</v>
       </c>
       <c r="AJ49" t="n">
-        <v>2.3</v>
+        <v>2.6</v>
       </c>
       <c r="AK49" s="3" t="n">
         <v>45646.69791666666</v>
@@ -6954,7 +6954,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6964,25 +6964,25 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="G51" t="n">
         <v>0</v>
       </c>
       <c r="H51" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I51" t="n">
         <v>0</v>
       </c>
       <c r="J51" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K51" t="inlineStr">
         <is>
@@ -6990,83 +6990,83 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M51" t="n">
-        <v>4.2</v>
+        <v>3.6</v>
       </c>
       <c r="N51" t="n">
-        <v>1.61</v>
+        <v>1.91</v>
       </c>
       <c r="O51" t="n">
-        <v>5.5</v>
+        <v>4.5</v>
       </c>
       <c r="P51" t="n">
-        <v>2.38</v>
+        <v>2.2</v>
       </c>
       <c r="Q51" t="n">
-        <v>2.1</v>
+        <v>2.6</v>
       </c>
       <c r="R51" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="S51" t="n">
-        <v>3.25</v>
+        <v>2.75</v>
       </c>
       <c r="T51" t="n">
-        <v>2.63</v>
+        <v>3</v>
       </c>
       <c r="U51" t="n">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="V51" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="W51" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="X51" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="Y51" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="Z51" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AA51" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AB51" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AC51" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AD51" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AE51" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF51" t="inlineStr">
+        <is>
+          <t>['12', '32', '38', '72']</t>
+        </is>
+      </c>
+      <c r="AG51" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AH51" t="n">
         <v>1.22</v>
       </c>
-      <c r="X51" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="Y51" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="Z51" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AA51" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AB51" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AC51" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AD51" t="n">
-        <v>2</v>
-      </c>
-      <c r="AE51" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF51" t="inlineStr">
-        <is>
-          <t>['56']</t>
-        </is>
-      </c>
-      <c r="AG51" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AH51" t="n">
-        <v>1.15</v>
-      </c>
       <c r="AI51" t="n">
-        <v>3.1</v>
+        <v>2.6</v>
       </c>
       <c r="AJ51" t="n">
-        <v>1.4</v>
+        <v>1.67</v>
       </c>
       <c r="AK51" s="3" t="n">
         <v>45646.69791666666</v>
@@ -7083,7 +7083,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -7093,109 +7093,109 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="G52" t="n">
+        <v>1</v>
+      </c>
+      <c r="H52" t="n">
+        <v>1</v>
+      </c>
+      <c r="I52" t="n">
+        <v>1</v>
+      </c>
+      <c r="J52" t="n">
+        <v>0</v>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L52" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="M52" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="N52" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="O52" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="P52" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="R52" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S52" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="T52" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="U52" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V52" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W52" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="X52" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="Y52" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="Z52" t="n">
         <v>2</v>
       </c>
-      <c r="H52" t="n">
-        <v>1</v>
-      </c>
-      <c r="I52" t="n">
-        <v>1</v>
-      </c>
-      <c r="J52" t="n">
-        <v>1</v>
-      </c>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L52" t="n">
+      <c r="AA52" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AB52" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AC52" t="n">
         <v>1.8</v>
       </c>
-      <c r="M52" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="N52" t="n">
-        <v>4</v>
-      </c>
-      <c r="O52" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="P52" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Q52" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="R52" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S52" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="T52" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="U52" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="V52" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W52" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="X52" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="Y52" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="Z52" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AA52" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AB52" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AC52" t="n">
+      <c r="AD52" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AE52" t="inlineStr">
+        <is>
+          <t>['17']</t>
+        </is>
+      </c>
+      <c r="AF52" t="inlineStr">
+        <is>
+          <t>['74']</t>
+        </is>
+      </c>
+      <c r="AG52" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AH52" t="n">
         <v>1.57</v>
       </c>
-      <c r="AD52" t="n">
+      <c r="AI52" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AJ52" t="n">
         <v>2.25</v>
-      </c>
-      <c r="AE52" t="inlineStr">
-        <is>
-          <t>['11', '75']</t>
-        </is>
-      </c>
-      <c r="AF52" t="inlineStr">
-        <is>
-          <t>['34']</t>
-        </is>
-      </c>
-      <c r="AG52" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AH52" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AI52" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AJ52" t="n">
-        <v>2.6</v>
       </c>
       <c r="AK52" s="3" t="n">
         <v>45646.69791666666</v>
@@ -7470,7 +7470,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -7480,25 +7480,25 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>KVC Westerlo</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>KV Mechelen</t>
         </is>
       </c>
       <c r="G55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H55" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I55" t="n">
         <v>0</v>
       </c>
       <c r="J55" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K55" t="inlineStr">
         <is>
@@ -7506,83 +7506,83 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>4</v>
+        <v>2.1</v>
       </c>
       <c r="M55" t="n">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="N55" t="n">
-        <v>1.91</v>
+        <v>3.1</v>
       </c>
       <c r="O55" t="n">
-        <v>4.5</v>
+        <v>2.7</v>
       </c>
       <c r="P55" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="R55" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S55" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="T55" t="n">
         <v>2.2</v>
       </c>
-      <c r="Q55" t="n">
+      <c r="U55" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="V55" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W55" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="X55" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y55" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Z55" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AA55" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AB55" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AC55" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AD55" t="n">
         <v>2.6</v>
       </c>
-      <c r="R55" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S55" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="T55" t="n">
-        <v>3</v>
-      </c>
-      <c r="U55" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V55" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W55" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="X55" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="Y55" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="Z55" t="n">
+      <c r="AE55" t="inlineStr">
+        <is>
+          <t>['75']</t>
+        </is>
+      </c>
+      <c r="AF55" t="inlineStr">
+        <is>
+          <t>['35']</t>
+        </is>
+      </c>
+      <c r="AG55" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AH55" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AI55" t="n">
         <v>1.8</v>
       </c>
-      <c r="AA55" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AB55" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AC55" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AD55" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AE55" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF55" t="inlineStr">
-        <is>
-          <t>['12', '32', '38', '72']</t>
-        </is>
-      </c>
-      <c r="AG55" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AH55" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AI55" t="n">
-        <v>2.6</v>
-      </c>
       <c r="AJ55" t="n">
-        <v>1.67</v>
+        <v>2.15</v>
       </c>
       <c r="AK55" s="3" t="n">
         <v>45646.69791666666</v>
@@ -7599,7 +7599,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7609,22 +7609,22 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="G56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H56" t="n">
         <v>1</v>
       </c>
       <c r="I56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -7635,83 +7635,83 @@
         </is>
       </c>
       <c r="L56" t="n">
+        <v>5</v>
+      </c>
+      <c r="M56" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="N56" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="O56" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="P56" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="R56" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S56" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T56" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="U56" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V56" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W56" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="X56" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="Y56" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="Z56" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AA56" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AB56" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AC56" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AD56" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE56" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF56" t="inlineStr">
+        <is>
+          <t>['56']</t>
+        </is>
+      </c>
+      <c r="AG56" t="n">
         <v>2.4</v>
       </c>
-      <c r="M56" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="N56" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="O56" t="n">
+      <c r="AH56" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AI56" t="n">
         <v>3.1</v>
       </c>
-      <c r="P56" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Q56" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="R56" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S56" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="T56" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="U56" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V56" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="W56" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="X56" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="Y56" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="Z56" t="n">
-        <v>2</v>
-      </c>
-      <c r="AA56" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AB56" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AC56" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AD56" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AE56" t="inlineStr">
-        <is>
-          <t>['17']</t>
-        </is>
-      </c>
-      <c r="AF56" t="inlineStr">
-        <is>
-          <t>['74']</t>
-        </is>
-      </c>
-      <c r="AG56" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AH56" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AI56" t="n">
-        <v>1.8</v>
-      </c>
       <c r="AJ56" t="n">
-        <v>2.25</v>
+        <v>1.4</v>
       </c>
       <c r="AK56" s="3" t="n">
         <v>45646.69791666666</v>
